--- a/raw/1964election.xlsx
+++ b/raw/1964election.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Dropbox/MyData/USvoting/historical voting/1920to1974/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C8E923-9BA9-944F-9343-4A910A742C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EB3553-FD5C-6D4C-A222-709206178204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="16500" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6268" uniqueCount="1960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6266" uniqueCount="1960">
   <si>
     <t>State</t>
   </si>
@@ -28965,8 +28965,8 @@
       <c r="C986" t="s">
         <v>7</v>
       </c>
-      <c r="D986" t="s">
-        <v>8</v>
+      <c r="D986">
+        <v>7</v>
       </c>
       <c r="E986" t="s">
         <v>1328</v>
@@ -29080,8 +29080,8 @@
       <c r="C991" t="s">
         <v>7</v>
       </c>
-      <c r="D991" t="s">
-        <v>17</v>
+      <c r="D991">
+        <v>9</v>
       </c>
       <c r="E991" t="s">
         <v>1335</v>
